--- a/StructureDefinition-SEEHDSLMCareDocumentation.xlsx
+++ b/StructureDefinition-SEEHDSLMCareDocumentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:04:04+00:00</t>
+    <t>2026-10-06T07:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMCareDocumentation.xlsx
+++ b/StructureDefinition-SEEHDSLMCareDocumentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:20:43+00:00</t>
+    <t>2026-10-07T11:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMCareDocumentation.xlsx
+++ b/StructureDefinition-SEEHDSLMCareDocumentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:41:58+00:00</t>
+    <t>2026-10-07T11:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMCareDocumentation.xlsx
+++ b/StructureDefinition-SEEHDSLMCareDocumentation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2681" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2806" uniqueCount="295">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:49:57+00:00</t>
+    <t>2026-10-09T07:52:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -262,8 +262,7 @@
     <t>Journalanteckning</t>
   </si>
   <si>
-    <t>De anteckningar som matchar begäran. En instans per anteckning.
-Kardinalitet: Valfri, lista.</t>
+    <t>De anteckningar som matchar begäran. En instans per anteckning.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -355,8 +354,7 @@
     <t>JoL-header</t>
   </si>
   <si>
-    <t>JoL-header v2.2. Innehåller metainformation gemensam för JoL-tjänstekontrakt.
-Kardinalitet: Obligatorisk.</t>
+    <t>JoL-header v2.2. Innehåller metainformation gemensam för JoL-tjänstekontrakt.</t>
   </si>
   <si>
     <t>SEEHDSLMCareDocumentation.careDocumentation.header.id</t>
@@ -375,8 +373,7 @@
   </si>
   <si>
     <t>Information för kontroll av åtkomst enligt PDL. Uppgifterna krävs för
-spärrhantering, åtkomstkontroll samt loggning.
-Kardinalitet: Obligatorisk.</t>
+spärrhantering, åtkomstkontroll samt loggning.</t>
   </si>
   <si>
     <t>SEEHDSLMCareDocumentation.careDocumentation.header.accessControlHeader.id</t>
@@ -391,15 +388,14 @@
     <t>SEEHDSLMCareDocumentation.careDocumentation.header.accessControlHeader.accountableHealthcareProvider</t>
   </si>
   <si>
-    <t xml:space="preserve">Identifier
+    <t xml:space="preserve">https://fhir.inera.se/ig/ehds-tk/StructureDefinition/SEEHDSRivIITypeHealthcondDescription3
 </t>
   </si>
   <si>
     <t>Informationsägande vårdgivare</t>
   </si>
   <si>
-    <t>Id för informationsägande vårdgivare. HSA-id eller lokalt id.
-Kardinalitet: Valfri.</t>
+    <t>Id för informationsägande vårdgivare. HSA-id eller lokalt id.</t>
   </si>
   <si>
     <t>SEEHDSLMCareDocumentation.careDocumentation.header.accessControlHeader.accountableCareUnit</t>
@@ -408,8 +404,7 @@
     <t>Informationsägande vårdenhet</t>
   </si>
   <si>
-    <t>Id för informationsägande vårdenhet angivet med HSA-id.
-Kardinalitet: Valfri.</t>
+    <t>Id för informationsägande vårdenhet angivet med HSA-id.</t>
   </si>
   <si>
     <t>SEEHDSLMCareDocumentation.careDocumentation.header.accessControlHeader.patientId</t>
@@ -418,8 +413,7 @@
     <t>Patientens identitetsbeteckning</t>
   </si>
   <si>
-    <t>Patientens identitetsbeteckning. Personnummer, samordningsnummer eller nationellt reservnummer.
-Kardinalitet: Obligatorisk.</t>
+    <t>Patientens identitetsbeteckning. Personnummer, samordningsnummer eller nationellt reservnummer.</t>
   </si>
   <si>
     <t>SEEHDSLMCareDocumentation.careDocumentation.header.accessControlHeader.careProcessId</t>
@@ -428,14 +422,13 @@
     <t>Id för individanpassad vårdprocess</t>
   </si>
   <si>
-    <t>Id för den individanpassade vårdprocess som informationen ingår i.
-Kardinalitet: Valfri.</t>
+    <t>Id för den individanpassade vårdprocess som informationen ingår i.</t>
   </si>
   <si>
     <t>SEEHDSLMCareDocumentation.careDocumentation.header.accessControlHeader.blockComparisonTime</t>
   </si>
   <si>
-    <t xml:space="preserve">dateTime
+    <t xml:space="preserve">https://fhir.inera.se/ig/ehds-tk/StructureDefinition/SEEHDSRivTimeStamp
 </t>
   </si>
   <si>
@@ -443,13 +436,14 @@
   </si>
   <si>
     <t>Den tidpunkt mot vilken spärrkontroll sker vid åtkomst till journalinformation.
-Format: YYYYMMDDhhmmss. Kardinalitet: Obligatorisk.</t>
+Format: YYYYMMDDhhmmss. Kardinalitet: Obligatorisk.
+Format enligt XSD (TimeStampType): ÅÅÅÅMMDDttmmss.</t>
   </si>
   <si>
     <t>SEEHDSLMCareDocumentation.careDocumentation.header.accessControlHeader.approvedForPatient</t>
   </si>
   <si>
-    <t xml:space="preserve">boolean
+    <t xml:space="preserve">https://fhir.inera.se/ig/ehds-tk/StructureDefinition/SEEHDSRivBoolean
 </t>
   </si>
   <si>
@@ -457,8 +451,7 @@
   </si>
   <si>
     <t>Ansvarig vårdpersonals beslut, alternativt baserat på automatisk menprövning,
-om informationen är godkänd för visning till patient.
-Kardinalitet: Obligatorisk.</t>
+om informationen är godkänd för visning till patient.</t>
   </si>
   <si>
     <t>SEEHDSLMCareDocumentation.careDocumentation.header.sourceSystemId</t>
@@ -467,8 +460,7 @@
     <t>Källsystem</t>
   </si>
   <si>
-    <t>Det källsystem som informationen lagras i. Fältet root sätts till HSA-id för källsystemet.
-Kardinalitet: Obligatorisk.</t>
+    <t>Det källsystem som informationen lagras i. Fältet root sätts till HSA-id för källsystemet.</t>
   </si>
   <si>
     <t>SEEHDSLMCareDocumentation.careDocumentation.header.record</t>
@@ -477,8 +469,7 @@
     <t>Uppgift i patientjournal</t>
   </si>
   <si>
-    <t>Metainformation avseende journaluppgiften (recorden).
-Kardinalitet: Obligatorisk.</t>
+    <t>Metainformation avseende journaluppgiften (recorden).</t>
   </si>
   <si>
     <t>SEEHDSLMCareDocumentation.careDocumentation.header.record.id</t>
@@ -490,15 +481,14 @@
     <t>SEEHDSLMCareDocumentation.careDocumentation.header.record.modifierExtension</t>
   </si>
   <si>
-    <t>SEEHDSLMCareDocumentation.careDocumentation.header.record.recordId</t>
+    <t>SEEHDSLMCareDocumentation.careDocumentation.header.record.rivId</t>
   </si>
   <si>
     <t>Journaluppgiftens unika identifierare</t>
   </si>
   <si>
     <t>Unik och beständig identifierare för uppgift i patientjournal.
-Ska vara unik — samma id får inte förekomma flera gånger (XSD-regel).
-Kardinalitet: Obligatorisk.</t>
+Ska vara unik — samma id får inte förekomma flera gånger (XSD-regel).</t>
   </si>
   <si>
     <t>SEEHDSLMCareDocumentation.careDocumentation.header.record.timestamp</t>
@@ -508,7 +498,8 @@
   </si>
   <si>
     <t>Första tidpunkten då denna journalinformation skapades.
-Format: YYYYMMDDhhmmss. Kardinalitet: Obligatorisk.</t>
+Format: YYYYMMDDhhmmss. Kardinalitet: Obligatorisk.
+Format enligt XSD (TimeStampType): ÅÅÅÅMMDDttmmss.</t>
   </si>
   <si>
     <t>SEEHDSLMCareDocumentation.careDocumentation.header.author</t>
@@ -517,8 +508,7 @@
     <t>Dokumentationsansvarig</t>
   </si>
   <si>
-    <t>Hälso- och sjukvårdspersonal som ansvarar för informationen i journaluppgiften.
-Kardinalitet: Valfri.</t>
+    <t>Hälso- och sjukvårdspersonal som ansvarar för informationen i journaluppgiften.</t>
   </si>
   <si>
     <t>SEEHDSLMCareDocumentation.careDocumentation.header.author.id</t>
@@ -530,24 +520,26 @@
     <t>SEEHDSLMCareDocumentation.careDocumentation.header.author.modifierExtension</t>
   </si>
   <si>
-    <t>SEEHDSLMCareDocumentation.careDocumentation.header.author.authorId</t>
+    <t>SEEHDSLMCareDocumentation.careDocumentation.header.author.rivId</t>
   </si>
   <si>
     <t>HSA-id för dokumentationsansvarig</t>
   </si>
   <si>
-    <t>HSA-id för hälso- och sjukvårdspersonal. Fältet root sätts till OID för HSA-id.
-Kardinalitet: Valfri.</t>
+    <t>HSA-id för hälso- och sjukvårdspersonal. Fältet root sätts till OID för HSA-id.</t>
   </si>
   <si>
     <t>SEEHDSLMCareDocumentation.careDocumentation.header.author.name</t>
   </si>
   <si>
+    <t xml:space="preserve">https://fhir.inera.se/ig/ehds-tk/StructureDefinition/SEEHDSRivString
+</t>
+  </si>
+  <si>
     <t>Namn på dokumentationsansvarig</t>
   </si>
   <si>
-    <t>Namn på hälso- och sjukvårdspersonal.
-Kardinalitet: Valfri.</t>
+    <t>Namn på hälso- och sjukvårdspersonal.</t>
   </si>
   <si>
     <t>SEEHDSLMCareDocumentation.careDocumentation.header.author.timestamp</t>
@@ -557,21 +549,21 @@
   </si>
   <si>
     <t>Tidpunkt vid vilken journalinformationen skapades av författaren.
-Format: YYYYMMDDhhmmss. Kardinalitet: Obligatorisk.</t>
+Format: YYYYMMDDhhmmss. Kardinalitet: Obligatorisk.
+Format enligt XSD (TimeStampType): ÅÅÅÅMMDDttmmss.</t>
   </si>
   <si>
     <t>SEEHDSLMCareDocumentation.careDocumentation.header.author.byRole</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept
+    <t xml:space="preserve">https://fhir.inera.se/ig/ehds-tk/StructureDefinition/SEEHDSRivCVTypeHealthcondDescription3
 </t>
   </si>
   <si>
     <t>Befattning</t>
   </si>
   <si>
-    <t>Information om hälso- och sjukvårdspersonalens befattning vid tidpunkten för dokumentationen.
-Kardinalitet: Valfri.</t>
+    <t>Information om hälso- och sjukvårdspersonalens befattning vid tidpunkten för dokumentationen.</t>
   </si>
   <si>
     <t>SEEHDSLMCareDocumentation.careDocumentation.header.author.orgUnit</t>
@@ -580,8 +572,7 @@
     <t>Organisationsenhet</t>
   </si>
   <si>
-    <t>Den organisation som författaren är uppdragstagare i vid dokumentationstillfället.
-Kardinalitet: Valfri.</t>
+    <t>Den organisation som författaren är uppdragstagare i vid dokumentationstillfället.</t>
   </si>
   <si>
     <t>SEEHDSLMCareDocumentation.careDocumentation.header.author.orgUnit.id</t>
@@ -599,8 +590,7 @@
     <t>HSA-id för organisationsenhet</t>
   </si>
   <si>
-    <t>HSA-id för organisationsenhet.
-Kardinalitet: Valfri (OrgUnitType-konvention).</t>
+    <t>HSA-id för organisationsenhet.</t>
   </si>
   <si>
     <t>SEEHDSLMCareDocumentation.careDocumentation.header.author.orgUnit.orgUnitName</t>
@@ -609,8 +599,43 @@
     <t>Namn på organisationsenhet</t>
   </si>
   <si>
-    <t>Namn på den organisation som författaren är uppdragstagare i.
-Kardinalitet: Valfri.</t>
+    <t>Namn på den organisation som författaren är uppdragstagare i.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareDocumentation.careDocumentation.header.author.orgUnit.orgUnitTelecom</t>
+  </si>
+  <si>
+    <t>Telefon till organisationsenhet</t>
+  </si>
+  <si>
+    <t>Telefon till organisationsenhet.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareDocumentation.careDocumentation.header.author.orgUnit.orgUnitEmail</t>
+  </si>
+  <si>
+    <t>E-post till organisationsenhet</t>
+  </si>
+  <si>
+    <t>Epost till organisationsenhet.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareDocumentation.careDocumentation.header.author.orgUnit.orgUnitAddress</t>
+  </si>
+  <si>
+    <t>Postadress till organisationsenhet</t>
+  </si>
+  <si>
+    <t>Postadress till organisationsenhet. Skrivs på ett så naturligt sätt som möjligt, exempelvis:”Storgatan 12468 91 Lilleby”</t>
+  </si>
+  <si>
+    <t>SEEHDSLMCareDocumentation.careDocumentation.header.author.orgUnit.orgUnitLocation</t>
+  </si>
+  <si>
+    <t>Plats för organisationsenhet</t>
+  </si>
+  <si>
+    <t>Text som anger namnet på plats eller ort för enhetens eller funktionens fysiska placering</t>
   </si>
   <si>
     <t>SEEHDSLMCareDocumentation.careDocumentation.header.signature</t>
@@ -619,8 +644,7 @@
     <t>Signeringsinformation</t>
   </si>
   <si>
-    <t>Signeringsinformation för journaluppgiften.
-Kardinalitet: Valfri.</t>
+    <t>Signeringsinformation för journaluppgiften.</t>
   </si>
   <si>
     <t>SEEHDSLMCareDocumentation.careDocumentation.header.signature.id</t>
@@ -632,14 +656,13 @@
     <t>SEEHDSLMCareDocumentation.careDocumentation.header.signature.modifierExtension</t>
   </si>
   <si>
-    <t>SEEHDSLMCareDocumentation.careDocumentation.header.signature.signatureId</t>
+    <t>SEEHDSLMCareDocumentation.careDocumentation.header.signature.rivId</t>
   </si>
   <si>
     <t>HSA-id för signerande person</t>
   </si>
   <si>
-    <t>HSA-id för hälso- och sjukvårdspersonal som signerat journaluppgiften.
-Kardinalitet: Valfri.</t>
+    <t>HSA-id för hälso- och sjukvårdspersonal som signerat journaluppgiften.</t>
   </si>
   <si>
     <t>SEEHDSLMCareDocumentation.careDocumentation.header.signature.name</t>
@@ -648,8 +671,7 @@
     <t>Namn på signerande person</t>
   </si>
   <si>
-    <t>Namn på hälso- och sjukvårdspersonal som signerat journaluppgiften.
-Kardinalitet: Valfri.</t>
+    <t>Namn på hälso- och sjukvårdspersonal som signerat journaluppgiften.</t>
   </si>
   <si>
     <t>SEEHDSLMCareDocumentation.careDocumentation.header.signature.timestamp</t>
@@ -659,7 +681,9 @@
   </si>
   <si>
     <t>Anger tidpunkten för signering av uppgift i patientjournal.
-Format: YYYYMMDDhhmmss. Kardinalitet: Valfri.</t>
+Format: YYYYMMDDhhmmss. Kardinalitet: Valfri.
+TKB anger kardinaliteten 0..1, men XSD:n kräver 1..1. Modellen följer XSD:n.
+Format enligt XSD (TimeStampType): ÅÅÅÅMMDDttmmss.</t>
   </si>
   <si>
     <t>SEEHDSLMCareDocumentation.careDocumentation.header.signature.byRole</t>
@@ -668,8 +692,7 @@
     <t>Befattning vid signering</t>
   </si>
   <si>
-    <t>Information om signerande persons befattning.
-Kardinalitet: Valfri.</t>
+    <t>Information om signerande persons befattning.</t>
   </si>
   <si>
     <t>SEEHDSLMCareDocumentation.careDocumentation.body</t>
@@ -678,8 +701,7 @@
     <t>Journalanteckningens innehåll</t>
   </si>
   <si>
-    <t>Journalanteckning — informationsinnehållet i anteckningen.
-Kardinalitet: Obligatorisk.</t>
+    <t>Journalanteckning — informationsinnehållet i anteckningen.</t>
   </si>
   <si>
     <t>getcaredocumentation-body-xor:Antingen clinicalDocumentNoteText eller multimediaEntry ska anges, ej båda {clinicalDocumentNoteText.exists() xor multimediaEntry.exists()}
@@ -702,13 +724,7 @@
   </si>
   <si>
     <t>Typ av anteckning. Kod tas från KV Anteckningstyp (OID: 1.2.752.129.2.2.2.11).
-Kardinalitet: Obligatorisk.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>https://fhir.inera.se/ig/ehds-tk/ValueSet/clinicaldocumentnotecode-vs</t>
+Kodverk/värdemängd: ClinicalDocumentNoteCodeVS.</t>
   </si>
   <si>
     <t>SEEHDSLMCareDocumentation.careDocumentation.body.clinicalDocumentNoteTitle</t>
@@ -717,8 +733,7 @@
     <t>Rubrik på anteckningen</t>
   </si>
   <si>
-    <t>Titel på anteckningen.
-Kardinalitet: Valfri.</t>
+    <t>Titel på anteckningen.</t>
   </si>
   <si>
     <t>SEEHDSLMCareDocumentation.careDocumentation.body.clinicalDocumentNoteText</t>
@@ -728,8 +743,7 @@
   </si>
   <si>
     <t>Journalanteckningens innehåll i text. Texten kan vara formaterad i DocBook-format
-och ska då vara 'entity encoded'. Ömsesidigt uteslutande med multimediaEntry.
-Kardinalitet: Valfri. XSD-regel: exakt ett av clinicalDocumentNoteText/multimediaEntry ska anges.</t>
+och ska då vara 'entity encoded'. Ömsesidigt uteslutande med multimediaEntry.</t>
   </si>
   <si>
     <t>SEEHDSLMCareDocumentation.careDocumentation.body.multimediaEntry</t>
@@ -739,8 +753,7 @@
   </si>
   <si>
     <t>Journalanteckningens innehåll i form av en multimediafil.
-Ömsesidigt uteslutande med clinicalDocumentNoteText.
-Kardinalitet: Valfri. XSD-regel: exakt ett av clinicalDocumentNoteText/multimediaEntry ska anges.</t>
+Ömsesidigt uteslutande med clinicalDocumentNoteText.</t>
   </si>
   <si>
     <t>getcaredocumentation-multimedia-xor:Antingen value eller reference ska anges i multimediaEntry, ej båda {value.exists() xor reference.exists()}
@@ -762,36 +775,33 @@
     <t>Medietyp</t>
   </si>
   <si>
-    <t>Typ av multimedia (MIME-typ). Tillåtna värden enligt MediaTypeEnum.
-Kardinalitet: Obligatorisk.</t>
+    <t>Typ av multimedia (MIME-typ). Tillåtna värden enligt MediaTypeEnum.</t>
   </si>
   <si>
     <t>SEEHDSLMCareDocumentation.careDocumentation.body.multimediaEntry.value</t>
   </si>
   <si>
-    <t xml:space="preserve">base64Binary
+    <t xml:space="preserve">https://fhir.inera.se/ig/ehds-tk/StructureDefinition/SEEHDSRivBase64Binary
 </t>
   </si>
   <si>
     <t>Binärdata</t>
   </si>
   <si>
-    <t>Binärdata som representerar objektet. Ömsesidigt uteslutande med reference.
-Kardinalitet: Valfri.</t>
+    <t>Binärdata som representerar objektet. Ömsesidigt uteslutande med reference.</t>
   </si>
   <si>
     <t>SEEHDSLMCareDocumentation.careDocumentation.body.multimediaEntry.reference</t>
   </si>
   <si>
-    <t xml:space="preserve">url
+    <t xml:space="preserve">https://fhir.inera.se/ig/ehds-tk/StructureDefinition/SEEHDSRivAnyURI
 </t>
   </si>
   <si>
     <t>Referens till extern fil</t>
   </si>
   <si>
-    <t>Referens till extern binär fil i form av en URL. Ömsesidigt uteslutande med value.
-Kardinalitet: Valfri.</t>
+    <t>Referens till extern binär fil i form av en URL. Ömsesidigt uteslutande med value.</t>
   </si>
   <si>
     <t>SEEHDSLMCareDocumentation.careDocumentation.body.dissentingOpinion</t>
@@ -801,8 +811,7 @@
   </si>
   <si>
     <t>Om patienten eller någon för denna ansvarig person är av avvikande mening om
-någon del av journalanteckningen.
-Kardinalitet: Valfri, lista.</t>
+någon del av journalanteckningen.</t>
   </si>
   <si>
     <t>SEEHDSLMCareDocumentation.careDocumentation.body.dissentingOpinion.id</t>
@@ -820,8 +829,7 @@
     <t>Id för avvikande mening</t>
   </si>
   <si>
-    <t>En universellt unik identifierare för den avvikande meningen.
-Kardinalitet: Valfri.</t>
+    <t>En universellt unik identifierare för den avvikande meningen.</t>
   </si>
   <si>
     <t>SEEHDSLMCareDocumentation.careDocumentation.body.dissentingOpinion.authorTime</t>
@@ -831,7 +839,7 @@
   </si>
   <si>
     <t>Tidpunkten då den avvikande meningen författades. Format: YYYYMMDDhhmmss.
-Kardinalitet: Obligatorisk.</t>
+Format enligt XSD (TimeStampType): ÅÅÅÅMMDDttmmss.</t>
   </si>
   <si>
     <t>SEEHDSLMCareDocumentation.careDocumentation.body.dissentingOpinion.opinion</t>
@@ -840,8 +848,7 @@
     <t>Text för avvikande mening</t>
   </si>
   <si>
-    <t>Text som innehåller den avvikande meningen.
-Kardinalitet: Obligatorisk.</t>
+    <t>Text som innehåller den avvikande meningen.</t>
   </si>
   <si>
     <t>SEEHDSLMCareDocumentation.careDocumentation.body.dissentingOpinion.personId</t>
@@ -853,7 +860,7 @@
     <t>Id för författaren av den avvikande meningen.
 root sätts till OID för typ av identifierare. För personnummer: 1.2.752.129.2.1.3.1.
 extension sätts till personens identifierare (12 tecken).
-Kardinalitet: Obligatorisk.</t>
+Enligt TKB i detta sammanhang: extension 1..1.</t>
   </si>
   <si>
     <t>SEEHDSLMCareDocumentation.careDocumentation.body.dissentingOpinion.personName</t>
@@ -862,8 +869,7 @@
     <t>Namn på författare till avvikande mening</t>
   </si>
   <si>
-    <t>Namnet på författaren av den avvikande meningen.
-Kardinalitet: Obligatorisk.</t>
+    <t>Namnet på författaren av den avvikande meningen.</t>
   </si>
   <si>
     <t>SEEHDSLMCareDocumentation.hasMore</t>
@@ -873,8 +879,7 @@
   </si>
   <si>
     <t>Anges av tjänsteproducent när det finns ytterligare information att hämta
-(partiell datahämtning). Referensen ska vara giltig i minst en timme.
-Kardinalitet: Valfri, lista.</t>
+(partiell datahämtning). Referensen ska vara giltig i minst en timme.</t>
   </si>
   <si>
     <t>SEEHDSLMCareDocumentation.hasMore.id</t>
@@ -892,8 +897,7 @@
     <t>Logisk adress för partiell hämtning</t>
   </si>
   <si>
-    <t>Den logiska adressen till tjänsteproducenten som tillhandahåller resterande information.
-Kardinalitet: Obligatorisk.</t>
+    <t>Den logiska adressen till tjänsteproducenten som tillhandahåller resterande information.</t>
   </si>
   <si>
     <t>SEEHDSLMCareDocumentation.hasMore.reference</t>
@@ -902,8 +906,7 @@
     <t>Referens för partiell hämtning</t>
   </si>
   <si>
-    <t>En unik identifierare som tjänstekonsumenten anger i nästa anrop via hasMoreReference.
-Kardinalitet: Obligatorisk.</t>
+    <t>En unik identifierare som tjänstekonsumenten anger i nästa anrop via hasMoreReference.</t>
   </si>
   <si>
     <t>SEEHDSLMCareDocumentation.result</t>
@@ -912,8 +915,7 @@
     <t>Resultat</t>
   </si>
   <si>
-    <t>Innehåller information om det gick bra eller ej att besvara begäran.
-Kardinalitet: Obligatorisk.</t>
+    <t>Innehåller information om det gick bra eller ej att besvara begäran.</t>
   </si>
   <si>
     <t>SEEHDSLMCareDocumentation.result.id</t>
@@ -928,15 +930,11 @@
     <t>SEEHDSLMCareDocumentation.result.resultCode</t>
   </si>
   <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
     <t>Resultatkod</t>
   </si>
   <si>
     <t>Anger resultatet av besvarad förfrågan. Tillåtna värden: OK, INFO, ERROR.
-Kardinalitet: Obligatorisk.</t>
+Tillåtna värden enligt XSD: OK, ERROR, INFO.</t>
   </si>
   <si>
     <t>SEEHDSLMCareDocumentation.result.resultText</t>
@@ -945,8 +943,7 @@
     <t>Resultattext</t>
   </si>
   <si>
-    <t>Optionellt felmeddelande som innehåller information om eventuella fel.
-Kardinalitet: Valfri.</t>
+    <t>Optionellt felmeddelande som innehåller information om eventuella fel.</t>
   </si>
 </sst>
 </file>
@@ -1248,7 +1245,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ84"/>
+  <dimension ref="A1:AJ88"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="89.87890625" customWidth="true" bestFit="true"/>
@@ -1261,7 +1258,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="15.140625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="74.1328125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1276,7 +1273,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="55.4140625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -4556,13 +4553,13 @@
         <v>72</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>84</v>
+        <v>164</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4630,10 +4627,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4659,10 +4656,10 @@
         <v>132</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4713,7 +4710,7 @@
         <v>72</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>83</v>
@@ -4730,10 +4727,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4756,13 +4753,13 @@
         <v>72</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4813,7 +4810,7 @@
         <v>72</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>73</v>
@@ -4830,10 +4827,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4859,10 +4856,10 @@
         <v>78</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4913,7 +4910,7 @@
         <v>72</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>73</v>
@@ -4930,10 +4927,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5030,10 +5027,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5132,10 +5129,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5236,10 +5233,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5262,13 +5259,13 @@
         <v>72</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>119</v>
+        <v>164</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5319,7 +5316,7 @@
         <v>72</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>73</v>
@@ -5336,10 +5333,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5362,13 +5359,13 @@
         <v>72</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>84</v>
+        <v>164</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5419,7 +5416,7 @@
         <v>72</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>73</v>
@@ -5436,10 +5433,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5462,13 +5459,13 @@
         <v>72</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>78</v>
+        <v>164</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5519,7 +5516,7 @@
         <v>72</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>73</v>
@@ -5531,15 +5528,15 @@
         <v>72</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5562,13 +5559,13 @@
         <v>72</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>84</v>
+        <v>164</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>86</v>
+        <v>191</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5619,7 +5616,7 @@
         <v>72</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>87</v>
+        <v>189</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>73</v>
@@ -5636,21 +5633,21 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>72</v>
@@ -5662,17 +5659,15 @@
         <v>72</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>90</v>
+        <v>164</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>91</v>
+        <v>193</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>72</v>
@@ -5709,75 +5704,71 @@
         <v>72</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>97</v>
+        <v>192</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>90</v>
+        <v>164</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>102</v>
+        <v>196</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>104</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>72</v>
       </c>
@@ -5825,27 +5816,27 @@
         <v>72</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>105</v>
+        <v>195</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5868,13 +5859,13 @@
         <v>72</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -5925,7 +5916,7 @@
         <v>72</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>73</v>
@@ -5937,15 +5928,15 @@
         <v>72</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -5971,10 +5962,10 @@
         <v>84</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>195</v>
+        <v>85</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>196</v>
+        <v>86</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6025,7 +6016,7 @@
         <v>72</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>194</v>
+        <v>87</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>73</v>
@@ -6042,21 +6033,21 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>72</v>
@@ -6068,15 +6059,17 @@
         <v>72</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>132</v>
+        <v>90</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>198</v>
+        <v>91</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>72</v>
@@ -6113,71 +6106,75 @@
         <v>72</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>197</v>
+        <v>97</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>170</v>
+        <v>90</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>201</v>
+        <v>102</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>72</v>
       </c>
@@ -6225,27 +6222,27 @@
         <v>72</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>200</v>
+        <v>105</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6253,7 +6250,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>83</v>
@@ -6268,13 +6265,13 @@
         <v>72</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6325,10 +6322,10 @@
         <v>72</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>83</v>
@@ -6337,7 +6334,7 @@
         <v>72</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>206</v>
+        <v>72</v>
       </c>
     </row>
     <row r="51">
@@ -6368,13 +6365,13 @@
         <v>72</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>84</v>
+        <v>164</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>85</v>
+        <v>208</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>86</v>
+        <v>209</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6425,7 +6422,7 @@
         <v>72</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>87</v>
+        <v>207</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>73</v>
@@ -6442,21 +6439,21 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>72</v>
@@ -6468,17 +6465,15 @@
         <v>72</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>90</v>
+        <v>132</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>91</v>
+        <v>211</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>72</v>
@@ -6515,75 +6510,71 @@
         <v>72</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>97</v>
+        <v>210</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>90</v>
+        <v>171</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>102</v>
+        <v>214</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>104</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>72</v>
       </c>
@@ -6631,27 +6622,27 @@
         <v>72</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>105</v>
+        <v>213</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6674,13 +6665,13 @@
         <v>72</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>170</v>
+        <v>78</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -6707,11 +6698,13 @@
         <v>72</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="Y54" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z54" t="s" s="2">
-        <v>214</v>
+        <v>72</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>72</v>
@@ -6729,7 +6722,7 @@
         <v>72</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -6741,15 +6734,15 @@
         <v>72</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>72</v>
+        <v>219</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6775,10 +6768,10 @@
         <v>84</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>216</v>
+        <v>85</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>217</v>
+        <v>86</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -6829,7 +6822,7 @@
         <v>72</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>215</v>
+        <v>87</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>73</v>
@@ -6846,21 +6839,21 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>72</v>
@@ -6872,15 +6865,17 @@
         <v>72</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>219</v>
+        <v>91</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>72</v>
@@ -6917,71 +6912,75 @@
         <v>72</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>218</v>
+        <v>97</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>222</v>
+        <v>102</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>72</v>
       </c>
@@ -7029,27 +7028,27 @@
         <v>72</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>221</v>
+        <v>105</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>224</v>
+        <v>98</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7057,7 +7056,7 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>83</v>
@@ -7072,13 +7071,13 @@
         <v>72</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>84</v>
+        <v>171</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>85</v>
+        <v>224</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>86</v>
+        <v>225</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7129,10 +7128,10 @@
         <v>72</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>87</v>
+        <v>223</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>83</v>
@@ -7153,14 +7152,14 @@
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>72</v>
@@ -7172,17 +7171,15 @@
         <v>72</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>90</v>
+        <v>164</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>91</v>
+        <v>227</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>72</v>
@@ -7219,75 +7216,71 @@
         <v>72</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>97</v>
+        <v>226</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>90</v>
+        <v>164</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>102</v>
+        <v>230</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>104</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>72</v>
       </c>
@@ -7335,27 +7328,27 @@
         <v>72</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>105</v>
+        <v>229</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7363,7 +7356,7 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>83</v>
@@ -7378,13 +7371,13 @@
         <v>72</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -7435,10 +7428,10 @@
         <v>72</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>83</v>
@@ -7447,15 +7440,15 @@
         <v>72</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>72</v>
+        <v>235</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7478,13 +7471,13 @@
         <v>72</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>232</v>
+        <v>84</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>233</v>
+        <v>85</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>234</v>
+        <v>86</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -7535,7 +7528,7 @@
         <v>72</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>231</v>
+        <v>87</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>73</v>
@@ -7552,21 +7545,21 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>72</v>
@@ -7578,15 +7571,17 @@
         <v>72</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>236</v>
+        <v>90</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>237</v>
+        <v>91</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>72</v>
@@ -7623,43 +7618,43 @@
         <v>72</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>235</v>
+        <v>97</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -7672,22 +7667,26 @@
         <v>72</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>240</v>
+        <v>102</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>72</v>
       </c>
@@ -7735,7 +7734,7 @@
         <v>72</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>239</v>
+        <v>105</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>73</v>
@@ -7747,15 +7746,15 @@
         <v>72</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>81</v>
+        <v>98</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7763,7 +7762,7 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G65" t="s" s="2">
         <v>83</v>
@@ -7778,13 +7777,13 @@
         <v>72</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>84</v>
+        <v>164</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>85</v>
+        <v>240</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>86</v>
+        <v>241</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -7835,10 +7834,10 @@
         <v>72</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>87</v>
+        <v>239</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH65" t="s" s="2">
         <v>83</v>
@@ -7852,21 +7851,21 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>72</v>
@@ -7878,17 +7877,15 @@
         <v>72</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>90</v>
+        <v>243</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>91</v>
+        <v>244</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>72</v>
@@ -7925,75 +7922,71 @@
         <v>72</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>97</v>
+        <v>242</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>90</v>
+        <v>247</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>102</v>
+        <v>248</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>104</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>72</v>
       </c>
@@ -8041,27 +8034,27 @@
         <v>72</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>105</v>
+        <v>246</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8072,7 +8065,7 @@
         <v>73</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>72</v>
@@ -8084,13 +8077,13 @@
         <v>72</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -8141,27 +8134,27 @@
         <v>72</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8169,7 +8162,7 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>83</v>
@@ -8184,13 +8177,13 @@
         <v>72</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>132</v>
+        <v>84</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>249</v>
+        <v>85</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>250</v>
+        <v>86</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -8241,10 +8234,10 @@
         <v>72</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>248</v>
+        <v>87</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>83</v>
@@ -8258,21 +8251,21 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>72</v>
@@ -8284,15 +8277,17 @@
         <v>72</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>252</v>
+        <v>91</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>72</v>
@@ -8329,71 +8324,75 @@
         <v>72</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>251</v>
+        <v>97</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>255</v>
+        <v>102</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>72</v>
       </c>
@@ -8441,27 +8440,27 @@
         <v>72</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>254</v>
+        <v>105</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8469,7 +8468,7 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>83</v>
@@ -8484,13 +8483,13 @@
         <v>72</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -8541,10 +8540,10 @@
         <v>72</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH72" t="s" s="2">
         <v>83</v>
@@ -8558,10 +8557,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8569,10 +8568,10 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>72</v>
@@ -8584,13 +8583,13 @@
         <v>72</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -8641,27 +8640,27 @@
         <v>72</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8669,7 +8668,7 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>83</v>
@@ -8684,13 +8683,13 @@
         <v>72</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>84</v>
+        <v>164</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>85</v>
+        <v>263</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>86</v>
+        <v>264</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -8741,10 +8740,10 @@
         <v>72</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>87</v>
+        <v>262</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>83</v>
@@ -8758,21 +8757,21 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>72</v>
@@ -8784,17 +8783,15 @@
         <v>72</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>91</v>
+        <v>266</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>72</v>
@@ -8831,75 +8828,71 @@
         <v>72</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>97</v>
+        <v>265</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>90</v>
+        <v>164</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>102</v>
+        <v>269</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>104</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>72</v>
       </c>
@@ -8947,27 +8940,27 @@
         <v>72</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>105</v>
+        <v>268</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -8975,10 +8968,10 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>72</v>
@@ -8990,13 +8983,13 @@
         <v>72</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -9047,27 +9040,27 @@
         <v>72</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9075,7 +9068,7 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G78" t="s" s="2">
         <v>83</v>
@@ -9093,10 +9086,10 @@
         <v>84</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>270</v>
+        <v>85</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>271</v>
+        <v>86</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -9147,10 +9140,10 @@
         <v>72</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>269</v>
+        <v>87</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH78" t="s" s="2">
         <v>83</v>
@@ -9164,21 +9157,21 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>72</v>
@@ -9190,15 +9183,17 @@
         <v>72</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>273</v>
+        <v>91</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N79" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>72</v>
@@ -9235,71 +9230,75 @@
         <v>72</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>272</v>
+        <v>97</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>81</v>
+        <v>98</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="P80" t="s" s="2">
         <v>72</v>
       </c>
@@ -9347,38 +9346,38 @@
         <v>72</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>72</v>
@@ -9390,17 +9389,15 @@
         <v>72</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>90</v>
+        <v>164</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>91</v>
+        <v>278</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>72</v>
@@ -9437,75 +9434,71 @@
         <v>72</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>97</v>
+        <v>277</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>90</v>
+        <v>164</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>102</v>
+        <v>281</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>104</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="N82" s="2"/>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>72</v>
       </c>
@@ -9553,27 +9546,27 @@
         <v>72</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>105</v>
+        <v>280</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9596,13 +9589,13 @@
         <v>72</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>279</v>
+        <v>78</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -9653,7 +9646,7 @@
         <v>72</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>83</v>
@@ -9665,15 +9658,15 @@
         <v>72</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9699,10 +9692,10 @@
         <v>84</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>283</v>
+        <v>85</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>284</v>
+        <v>86</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -9753,7 +9746,7 @@
         <v>72</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>282</v>
+        <v>87</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>73</v>
@@ -9765,6 +9758,412 @@
         <v>72</v>
       </c>
       <c r="AJ84" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O85" s="2"/>
+      <c r="P85" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="P86" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
+      <c r="P87" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" s="2"/>
+      <c r="P88" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
         <v>72</v>
       </c>
     </row>

--- a/StructureDefinition-SEEHDSLMCareDocumentation.xlsx
+++ b/StructureDefinition-SEEHDSLMCareDocumentation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.3</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T07:52:45+00:00</t>
+    <t>2026-10-12T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMCareDocumentation.xlsx
+++ b/StructureDefinition-SEEHDSLMCareDocumentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:51:47+00:00</t>
+    <t>2026-10-12T13:38:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMCareDocumentation.xlsx
+++ b/StructureDefinition-SEEHDSLMCareDocumentation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:38:08+00:00</t>
+    <t>2026-10-15T17:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMCareDocumentation.xlsx
+++ b/StructureDefinition-SEEHDSLMCareDocumentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T17:10:15+00:00</t>
+    <t>2026-10-15T18:03:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMCareDocumentation.xlsx
+++ b/StructureDefinition-SEEHDSLMCareDocumentation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T18:03:33+00:00</t>
+    <t>2026-10-26T15:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
